--- a/Planning_ST_Antoine_12oct-1nov.xlsx
+++ b/Planning_ST_Antoine_12oct-1nov.xlsx
@@ -77,18 +77,6 @@
       </text>
     </comment>
     <comment ref="C41" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Jour férié (Toussaint) : non travaillé</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K41" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2141,23 +2129,31 @@
         <v>12</v>
       </c>
       <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="15" t="str">
+      <c r="C22" s="14" t="n">
+        <v>0.486111111111111</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="15" t="n">
         <f aca="false">IF(C22="","",D22-C22)</f>
-        <v/>
-      </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="15" t="str">
+        <v>0.138888888888889</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0.819444444444444</v>
+      </c>
+      <c r="H22" s="15" t="n">
         <f aca="false">IF(F22="","",G22-F22)</f>
-        <v/>
-      </c>
-      <c r="I22" s="16" t="str">
+        <v>0.152777777777778</v>
+      </c>
+      <c r="I22" s="16" t="n">
         <f aca="false">IF(H22="",IF(E22="","",IF(E22&lt;$C$2,"# Matin 1",IF(E22&gt;$D$2,"# Matin 2",E22))
 ),IF(E22="",IF(H22&lt;$C$2,"# AprèsMidi 1",IF(H22&gt;$D$2,"# AprèsMidi 2",H22)
 ),IF(H22&gt;$D$2,"# AprèsMidi 2",IF(E22&gt;$D$2,"# Matin 2",IF((F22-D22)&gt;$B$2,"# Repas 1", IF((F22-D22)&lt;$A$2,"# Repas 2",IF((E22+H22)&lt;$E$2,"# Jour 1",IF((E22+H22)&gt;$F$2,"# Jour 2",E22+H22))))))))</f>
-        <v/>
+        <v>0.291666666666667</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="14" t="n">
@@ -2186,31 +2182,23 @@
 ),IF(P22&gt;$D$2,"# AprèsMidi 2",IF(M22&gt;$D$2,"# Matin 2",IF((N22-L22)&gt;$B$2,"# Repas 1", IF((N22-L22)&lt;$A$2,"# Repas 2",IF((M22+P22)&lt;$E$2,"# Jour 1",IF((M22+P22)&gt;$F$2,"# Jour 2",M22+P22))))))))</f>
         <v>0.291666666666667</v>
       </c>
-      <c r="S22" s="14" t="n">
-        <v>0.517361111111111</v>
-      </c>
-      <c r="T22" s="14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="U22" s="15" t="n">
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="15" t="str">
         <f aca="false">IF(S22="","",T22-S22)</f>
-        <v>0.107638888888889</v>
-      </c>
-      <c r="V22" s="14" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="W22" s="14" t="n">
-        <v>0.819444444444444</v>
-      </c>
-      <c r="X22" s="15" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="15" t="str">
         <f aca="false">IF(V22="","",W22-V22)</f>
-        <v>0.152777777777778</v>
-      </c>
-      <c r="Y22" s="16" t="n">
+        <v/>
+      </c>
+      <c r="Y22" s="16" t="str">
         <f aca="false">IF(X22="",IF(U22="","",IF(U22&lt;$C$2,"# Matin 1",IF(U22&gt;$D$2,"# Matin 2",U22))
 ),IF(U22="",IF(X22&lt;$C$2,"# AprèsMidi 1",IF(X22&gt;$D$2,"# AprèsMidi 2",X22)
 ),IF(X22&gt;$D$2,"# AprèsMidi 2",IF(U22&gt;$D$2,"# Matin 2",IF((V22-T22)&gt;$B$2,"# Repas 1", IF((V22-T22)&lt;$A$2,"# Repas 2",IF((U22+X22)&lt;$E$2,"# Jour 1",IF((U22+X22)&gt;$F$2,"# Jour 2",U22+X22))))))))</f>
-        <v>0.260416666666667</v>
+        <v/>
       </c>
       <c r="AA22" s="14"/>
       <c r="AB22" s="14"/>
@@ -2263,49 +2251,49 @@
         <v>0.291666666666667</v>
       </c>
       <c r="J23" s="3"/>
-      <c r="K23" s="14" t="n">
-        <v>0.486111111111111</v>
-      </c>
-      <c r="L23" s="14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="M23" s="15" t="n">
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="15" t="str">
         <f aca="false">IF(K23="","",L23-K23)</f>
-        <v>0.138888888888889</v>
-      </c>
-      <c r="N23" s="14" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="O23" s="14" t="n">
-        <v>0.819444444444444</v>
-      </c>
-      <c r="P23" s="15" t="n">
+        <v/>
+      </c>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="15" t="str">
         <f aca="false">IF(N23="","",O23-N23)</f>
-        <v>0.152777777777778</v>
-      </c>
-      <c r="Q23" s="16" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="16" t="str">
         <f aca="false">IF(P23="",IF(M23="","",IF(M23&lt;$C$2,"# Matin 1",IF(M23&gt;$D$2,"# Matin 2",M23))
 ),IF(M23="",IF(P23&lt;$C$2,"# AprèsMidi 1",IF(P23&gt;$D$2,"# AprèsMidi 2",P23)
 ),IF(P23&gt;$D$2,"# AprèsMidi 2",IF(M23&gt;$D$2,"# Matin 2",IF((N23-L23)&gt;$B$2,"# Repas 1", IF((N23-L23)&lt;$A$2,"# Repas 2",IF((M23+P23)&lt;$E$2,"# Jour 1",IF((M23+P23)&gt;$F$2,"# Jour 2",M23+P23))))))))</f>
-        <v>0.291666666666667</v>
-      </c>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="15" t="str">
+        <v/>
+      </c>
+      <c r="S23" s="14" t="n">
+        <v>0.517361111111111</v>
+      </c>
+      <c r="T23" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="U23" s="15" t="n">
         <f aca="false">IF(S23="","",T23-S23)</f>
-        <v/>
-      </c>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="15" t="str">
+        <v>0.107638888888889</v>
+      </c>
+      <c r="V23" s="14" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="W23" s="14" t="n">
+        <v>0.819444444444444</v>
+      </c>
+      <c r="X23" s="15" t="n">
         <f aca="false">IF(V23="","",W23-V23)</f>
-        <v/>
-      </c>
-      <c r="Y23" s="16" t="str">
+        <v>0.152777777777778</v>
+      </c>
+      <c r="Y23" s="16" t="n">
         <f aca="false">IF(X23="",IF(U23="","",IF(U23&lt;$C$2,"# Matin 1",IF(U23&gt;$D$2,"# Matin 2",U23))
 ),IF(U23="",IF(X23&lt;$C$2,"# AprèsMidi 1",IF(X23&gt;$D$2,"# AprèsMidi 2",X23)
 ),IF(X23&gt;$D$2,"# AprèsMidi 2",IF(U23&gt;$D$2,"# Matin 2",IF((V23-T23)&gt;$B$2,"# Repas 1", IF((V23-T23)&lt;$A$2,"# Repas 2",IF((U23+X23)&lt;$E$2,"# Jour 1",IF((U23+X23)&gt;$F$2,"# Jour 2",U23+X23))))))))</f>
-        <v/>
+        <v>0.260416666666667</v>
       </c>
       <c r="AA23" s="14"/>
       <c r="AB23" s="14"/>
@@ -2427,24 +2415,24 @@
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="n">
-        <v>0.409722222222222</v>
+        <v>0.486111111111111</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>0.583333333333333</v>
+        <v>0.625</v>
       </c>
       <c r="E25" s="15" t="n">
         <f aca="false">IF(C25="","",D25-C25)</f>
-        <v>0.173611111111111</v>
+        <v>0.138888888888889</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>0.625</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>0.743055555555556</v>
+        <v>0.819444444444444</v>
       </c>
       <c r="H25" s="15" t="n">
         <f aca="false">IF(F25="","",G25-F25)</f>
-        <v>0.118055555555556</v>
+        <v>0.152777777777778</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">IF(H25="",IF(E25="","",IF(E25&lt;$C$2,"# Matin 1",IF(E25&gt;$D$2,"# Matin 2",E25))
@@ -2453,49 +2441,49 @@
         <v>0.291666666666667</v>
       </c>
       <c r="J25" s="3"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="15" t="str">
+      <c r="K25" s="14" t="n">
+        <v>0.409722222222222</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="M25" s="15" t="n">
         <f aca="false">IF(K25="","",L25-K25)</f>
-        <v/>
-      </c>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="15" t="str">
+        <v>0.173611111111111</v>
+      </c>
+      <c r="N25" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O25" s="14" t="n">
+        <v>0.743055555555556</v>
+      </c>
+      <c r="P25" s="15" t="n">
         <f aca="false">IF(N25="","",O25-N25)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="16" t="str">
+        <v>0.118055555555556</v>
+      </c>
+      <c r="Q25" s="16" t="n">
         <f aca="false">IF(P25="",IF(M25="","",IF(M25&lt;$C$2,"# Matin 1",IF(M25&gt;$D$2,"# Matin 2",M25))
 ),IF(M25="",IF(P25&lt;$C$2,"# AprèsMidi 1",IF(P25&gt;$D$2,"# AprèsMidi 2",P25)
 ),IF(P25&gt;$D$2,"# AprèsMidi 2",IF(M25&gt;$D$2,"# Matin 2",IF((N25-L25)&gt;$B$2,"# Repas 1", IF((N25-L25)&lt;$A$2,"# Repas 2",IF((M25+P25)&lt;$E$2,"# Jour 1",IF((M25+P25)&gt;$F$2,"# Jour 2",M25+P25))))))))</f>
-        <v/>
-      </c>
-      <c r="S25" s="14" t="n">
-        <v>0.517361111111111</v>
-      </c>
-      <c r="T25" s="14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="U25" s="15" t="n">
+        <v>0.291666666666667</v>
+      </c>
+      <c r="S25" s="14"/>
+      <c r="T25" s="14"/>
+      <c r="U25" s="15" t="str">
         <f aca="false">IF(S25="","",T25-S25)</f>
-        <v>0.107638888888889</v>
-      </c>
-      <c r="V25" s="14" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="W25" s="14" t="n">
-        <v>0.819444444444444</v>
-      </c>
-      <c r="X25" s="15" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="14"/>
+      <c r="W25" s="14"/>
+      <c r="X25" s="15" t="str">
         <f aca="false">IF(V25="","",W25-V25)</f>
-        <v>0.152777777777778</v>
-      </c>
-      <c r="Y25" s="16" t="n">
+        <v/>
+      </c>
+      <c r="Y25" s="16" t="str">
         <f aca="false">IF(X25="",IF(U25="","",IF(U25&lt;$C$2,"# Matin 1",IF(U25&gt;$D$2,"# Matin 2",U25))
 ),IF(U25="",IF(X25&lt;$C$2,"# AprèsMidi 1",IF(X25&gt;$D$2,"# AprèsMidi 2",X25)
 ),IF(X25&gt;$D$2,"# AprèsMidi 2",IF(U25&gt;$D$2,"# Matin 2",IF((V25-T25)&gt;$B$2,"# Repas 1", IF((V25-T25)&lt;$A$2,"# Repas 2",IF((U25+X25)&lt;$E$2,"# Jour 1",IF((U25+X25)&gt;$F$2,"# Jour 2",U25+X25))))))))</f>
-        <v>0.260416666666667</v>
+        <v/>
       </c>
       <c r="AA25" s="14"/>
       <c r="AB25" s="14"/>
@@ -2521,52 +2509,44 @@
         <v>16</v>
       </c>
       <c r="B26" s="13"/>
-      <c r="C26" s="14" t="n">
-        <v>0.409722222222222</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="E26" s="15" t="n">
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="15" t="str">
         <f aca="false">IF(C26="","",D26-C26)</f>
-        <v>0.173611111111111</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>0.743055555555556</v>
-      </c>
-      <c r="H26" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="15" t="str">
         <f aca="false">IF(F26="","",G26-F26)</f>
-        <v>0.118055555555556</v>
-      </c>
-      <c r="I26" s="16" t="n">
+        <v/>
+      </c>
+      <c r="I26" s="16" t="str">
         <f aca="false">IF(H26="",IF(E26="","",IF(E26&lt;$C$2,"# Matin 1",IF(E26&gt;$D$2,"# Matin 2",E26))
 ),IF(E26="",IF(H26&lt;$C$2,"# AprèsMidi 1",IF(H26&gt;$D$2,"# AprèsMidi 2",H26)
 ),IF(H26&gt;$D$2,"# AprèsMidi 2",IF(E26&gt;$D$2,"# Matin 2",IF((F26-D26)&gt;$B$2,"# Repas 1", IF((F26-D26)&lt;$A$2,"# Repas 2",IF((E26+H26)&lt;$E$2,"# Jour 1",IF((E26+H26)&gt;$F$2,"# Jour 2",E26+H26))))))))</f>
-        <v>0.291666666666667</v>
+        <v/>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="14" t="n">
-        <v>0.486111111111111</v>
+        <v>0.409722222222222</v>
       </c>
       <c r="L26" s="14" t="n">
-        <v>0.625</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="M26" s="15" t="n">
         <f aca="false">IF(K26="","",L26-K26)</f>
-        <v>0.138888888888889</v>
+        <v>0.173611111111111</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>0.666666666666667</v>
+        <v>0.625</v>
       </c>
       <c r="O26" s="14" t="n">
-        <v>0.819444444444444</v>
+        <v>0.743055555555556</v>
       </c>
       <c r="P26" s="15" t="n">
         <f aca="false">IF(N26="","",O26-N26)</f>
-        <v>0.152777777777778</v>
+        <v>0.118055555555556</v>
       </c>
       <c r="Q26" s="16" t="n">
         <f aca="false">IF(P26="",IF(M26="","",IF(M26&lt;$C$2,"# Matin 1",IF(M26&gt;$D$2,"# Matin 2",M26))
@@ -2574,23 +2554,31 @@
 ),IF(P26&gt;$D$2,"# AprèsMidi 2",IF(M26&gt;$D$2,"# Matin 2",IF((N26-L26)&gt;$B$2,"# Repas 1", IF((N26-L26)&lt;$A$2,"# Repas 2",IF((M26+P26)&lt;$E$2,"# Jour 1",IF((M26+P26)&gt;$F$2,"# Jour 2",M26+P26))))))))</f>
         <v>0.291666666666667</v>
       </c>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="15" t="str">
+      <c r="S26" s="14" t="n">
+        <v>0.517361111111111</v>
+      </c>
+      <c r="T26" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="U26" s="15" t="n">
         <f aca="false">IF(S26="","",T26-S26)</f>
-        <v/>
-      </c>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
-      <c r="X26" s="15" t="str">
+        <v>0.107638888888889</v>
+      </c>
+      <c r="V26" s="14" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="W26" s="14" t="n">
+        <v>0.819444444444444</v>
+      </c>
+      <c r="X26" s="15" t="n">
         <f aca="false">IF(V26="","",W26-V26)</f>
-        <v/>
-      </c>
-      <c r="Y26" s="16" t="str">
+        <v>0.152777777777778</v>
+      </c>
+      <c r="Y26" s="16" t="n">
         <f aca="false">IF(X26="",IF(U26="","",IF(U26&lt;$C$2,"# Matin 1",IF(U26&gt;$D$2,"# Matin 2",U26))
 ),IF(U26="",IF(X26&lt;$C$2,"# AprèsMidi 1",IF(X26&gt;$D$2,"# AprèsMidi 2",X26)
 ),IF(X26&gt;$D$2,"# AprèsMidi 2",IF(U26&gt;$D$2,"# Matin 2",IF((V26-T26)&gt;$B$2,"# Repas 1", IF((V26-T26)&lt;$A$2,"# Repas 2",IF((U26+X26)&lt;$E$2,"# Jour 1",IF((U26+X26)&gt;$F$2,"# Jour 2",U26+X26))))))))</f>
-        <v/>
+        <v>0.260416666666667</v>
       </c>
       <c r="AA26" s="14"/>
       <c r="AB26" s="14"/>
@@ -2617,24 +2605,24 @@
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="n">
-        <v>0.409722222222222</v>
+        <v>0.486111111111111</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>0.583333333333333</v>
+        <v>0.625</v>
       </c>
       <c r="E27" s="15" t="n">
         <f aca="false">IF(C27="","",D27-C27)</f>
-        <v>0.173611111111111</v>
+        <v>0.138888888888889</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>0.625</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>0.743055555555556</v>
+        <v>0.819444444444444</v>
       </c>
       <c r="H27" s="15" t="n">
         <f aca="false">IF(F27="","",G27-F27)</f>
-        <v>0.118055555555556</v>
+        <v>0.152777777777778</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">IF(H27="",IF(E27="","",IF(E27&lt;$C$2,"# Matin 1",IF(E27&gt;$D$2,"# Matin 2",E27))
@@ -2643,49 +2631,49 @@
         <v>0.291666666666667</v>
       </c>
       <c r="J27" s="3"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="15" t="str">
+      <c r="K27" s="14" t="n">
+        <v>0.409722222222222</v>
+      </c>
+      <c r="L27" s="14" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="M27" s="15" t="n">
         <f aca="false">IF(K27="","",L27-K27)</f>
-        <v/>
-      </c>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="15" t="str">
+        <v>0.173611111111111</v>
+      </c>
+      <c r="N27" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O27" s="14" t="n">
+        <v>0.743055555555556</v>
+      </c>
+      <c r="P27" s="15" t="n">
         <f aca="false">IF(N27="","",O27-N27)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="16" t="str">
+        <v>0.118055555555556</v>
+      </c>
+      <c r="Q27" s="16" t="n">
         <f aca="false">IF(P27="",IF(M27="","",IF(M27&lt;$C$2,"# Matin 1",IF(M27&gt;$D$2,"# Matin 2",M27))
 ),IF(M27="",IF(P27&lt;$C$2,"# AprèsMidi 1",IF(P27&gt;$D$2,"# AprèsMidi 2",P27)
 ),IF(P27&gt;$D$2,"# AprèsMidi 2",IF(M27&gt;$D$2,"# Matin 2",IF((N27-L27)&gt;$B$2,"# Repas 1", IF((N27-L27)&lt;$A$2,"# Repas 2",IF((M27+P27)&lt;$E$2,"# Jour 1",IF((M27+P27)&gt;$F$2,"# Jour 2",M27+P27))))))))</f>
-        <v/>
-      </c>
-      <c r="S27" s="14" t="n">
-        <v>0.517361111111111</v>
-      </c>
-      <c r="T27" s="14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="U27" s="15" t="n">
+        <v>0.291666666666667</v>
+      </c>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="15" t="str">
         <f aca="false">IF(S27="","",T27-S27)</f>
-        <v>0.107638888888889</v>
-      </c>
-      <c r="V27" s="14" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="W27" s="14" t="n">
-        <v>0.819444444444444</v>
-      </c>
-      <c r="X27" s="15" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="X27" s="15" t="str">
         <f aca="false">IF(V27="","",W27-V27)</f>
-        <v>0.152777777777778</v>
-      </c>
-      <c r="Y27" s="16" t="n">
+        <v/>
+      </c>
+      <c r="Y27" s="16" t="str">
         <f aca="false">IF(X27="",IF(U27="","",IF(U27&lt;$C$2,"# Matin 1",IF(U27&gt;$D$2,"# Matin 2",U27))
 ),IF(U27="",IF(X27&lt;$C$2,"# AprèsMidi 1",IF(X27&gt;$D$2,"# AprèsMidi 2",X27)
 ),IF(X27&gt;$D$2,"# AprèsMidi 2",IF(U27&gt;$D$2,"# Matin 2",IF((V27-T27)&gt;$B$2,"# Repas 1", IF((V27-T27)&lt;$A$2,"# Repas 2",IF((U27+X27)&lt;$E$2,"# Jour 1",IF((U27+X27)&gt;$F$2,"# Jour 2",U27+X27))))))))</f>
-        <v>0.260416666666667</v>
+        <v/>
       </c>
       <c r="AA27" s="14"/>
       <c r="AB27" s="14"/>
@@ -2738,49 +2726,49 @@
         <v>0.291666666666667</v>
       </c>
       <c r="J28" s="3"/>
-      <c r="K28" s="14" t="n">
-        <v>0.465277777777778</v>
-      </c>
-      <c r="L28" s="14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="M28" s="15" t="n">
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="15" t="str">
         <f aca="false">IF(K28="","",L28-K28)</f>
-        <v>0.159722222222222</v>
-      </c>
-      <c r="N28" s="14" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="O28" s="14" t="n">
-        <v>0.798611111111111</v>
-      </c>
-      <c r="P28" s="15" t="n">
+        <v/>
+      </c>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="15" t="str">
         <f aca="false">IF(N28="","",O28-N28)</f>
-        <v>0.131944444444444</v>
-      </c>
-      <c r="Q28" s="16" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="16" t="str">
         <f aca="false">IF(P28="",IF(M28="","",IF(M28&lt;$C$2,"# Matin 1",IF(M28&gt;$D$2,"# Matin 2",M28))
 ),IF(M28="",IF(P28&lt;$C$2,"# AprèsMidi 1",IF(P28&gt;$D$2,"# AprèsMidi 2",P28)
 ),IF(P28&gt;$D$2,"# AprèsMidi 2",IF(M28&gt;$D$2,"# Matin 2",IF((N28-L28)&gt;$B$2,"# Repas 1", IF((N28-L28)&lt;$A$2,"# Repas 2",IF((M28+P28)&lt;$E$2,"# Jour 1",IF((M28+P28)&gt;$F$2,"# Jour 2",M28+P28))))))))</f>
-        <v>0.291666666666667</v>
-      </c>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="15" t="str">
+        <v/>
+      </c>
+      <c r="S28" s="14" t="n">
+        <v>0.496527777777778</v>
+      </c>
+      <c r="T28" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="U28" s="15" t="n">
         <f aca="false">IF(S28="","",T28-S28)</f>
-        <v/>
-      </c>
-      <c r="V28" s="14"/>
-      <c r="W28" s="14"/>
-      <c r="X28" s="15" t="str">
+        <v>0.128472222222222</v>
+      </c>
+      <c r="V28" s="14" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="W28" s="14" t="n">
+        <v>0.798611111111111</v>
+      </c>
+      <c r="X28" s="15" t="n">
         <f aca="false">IF(V28="","",W28-V28)</f>
-        <v/>
-      </c>
-      <c r="Y28" s="16" t="str">
+        <v>0.131944444444444</v>
+      </c>
+      <c r="Y28" s="16" t="n">
         <f aca="false">IF(X28="",IF(U28="","",IF(U28&lt;$C$2,"# Matin 1",IF(U28&gt;$D$2,"# Matin 2",U28))
 ),IF(U28="",IF(X28&lt;$C$2,"# AprèsMidi 1",IF(X28&gt;$D$2,"# AprèsMidi 2",X28)
 ),IF(X28&gt;$D$2,"# AprèsMidi 2",IF(U28&gt;$D$2,"# Matin 2",IF((V28-T28)&gt;$B$2,"# Repas 1", IF((V28-T28)&lt;$A$2,"# Repas 2",IF((U28+X28)&lt;$E$2,"# Jour 1",IF((U28+X28)&gt;$F$2,"# Jour 2",U28+X28))))))))</f>
-        <v/>
+        <v>0.260416666666667</v>
       </c>
       <c r="AA28" s="14"/>
       <c r="AB28" s="14"/>
@@ -3193,24 +3181,24 @@
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="14" t="n">
-        <v>0.486111111111111</v>
+        <v>0.409722222222222</v>
       </c>
       <c r="L36" s="14" t="n">
-        <v>0.625</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="M36" s="15" t="n">
         <f aca="false">IF(K36="","",L36-K36)</f>
-        <v>0.138888888888889</v>
+        <v>0.173611111111111</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>0.666666666666667</v>
+        <v>0.625</v>
       </c>
       <c r="O36" s="14" t="n">
-        <v>0.819444444444444</v>
+        <v>0.743055555555556</v>
       </c>
       <c r="P36" s="15" t="n">
         <f aca="false">IF(N36="","",O36-N36)</f>
-        <v>0.152777777777778</v>
+        <v>0.118055555555556</v>
       </c>
       <c r="Q36" s="16" t="n">
         <f aca="false">IF(P36="",IF(M36="","",IF(M36&lt;$C$2,"# Matin 1",IF(M36&gt;$D$2,"# Matin 2",M36))
@@ -3218,23 +3206,31 @@
 ),IF(P36&gt;$D$2,"# AprèsMidi 2",IF(M36&gt;$D$2,"# Matin 2",IF((N36-L36)&gt;$B$2,"# Repas 1", IF((N36-L36)&lt;$A$2,"# Repas 2",IF((M36+P36)&lt;$E$2,"# Jour 1",IF((M36+P36)&gt;$F$2,"# Jour 2",M36+P36))))))))</f>
         <v>0.291666666666667</v>
       </c>
-      <c r="S36" s="14"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="15" t="str">
+      <c r="S36" s="14" t="n">
+        <v>0.517361111111111</v>
+      </c>
+      <c r="T36" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="U36" s="15" t="n">
         <f aca="false">IF(S36="","",T36-S36)</f>
-        <v/>
-      </c>
-      <c r="V36" s="14"/>
-      <c r="W36" s="14"/>
-      <c r="X36" s="15" t="str">
+        <v>0.107638888888889</v>
+      </c>
+      <c r="V36" s="14" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="W36" s="14" t="n">
+        <v>0.819444444444444</v>
+      </c>
+      <c r="X36" s="15" t="n">
         <f aca="false">IF(V36="","",W36-V36)</f>
-        <v/>
-      </c>
-      <c r="Y36" s="16" t="str">
+        <v>0.152777777777778</v>
+      </c>
+      <c r="Y36" s="16" t="n">
         <f aca="false">IF(X36="",IF(U36="","",IF(U36&lt;$C$2,"# Matin 1",IF(U36&gt;$D$2,"# Matin 2",U36))
 ),IF(U36="",IF(X36&lt;$C$2,"# AprèsMidi 1",IF(X36&gt;$D$2,"# AprèsMidi 2",X36)
 ),IF(X36&gt;$D$2,"# AprèsMidi 2",IF(U36&gt;$D$2,"# Matin 2",IF((V36-T36)&gt;$B$2,"# Repas 1", IF((V36-T36)&lt;$A$2,"# Repas 2",IF((U36+X36)&lt;$E$2,"# Jour 1",IF((U36+X36)&gt;$F$2,"# Jour 2",U36+X36))))))))</f>
-        <v/>
+        <v>0.260416666666667</v>
       </c>
       <c r="AA36" s="14"/>
       <c r="AB36" s="14"/>
@@ -3260,23 +3256,31 @@
         <v>14</v>
       </c>
       <c r="B37" s="13"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="15" t="str">
+      <c r="C37" s="14" t="n">
+        <v>0.486111111111111</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E37" s="15" t="n">
         <f aca="false">IF(C37="","",D37-C37)</f>
-        <v/>
-      </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="15" t="str">
+        <v>0.138888888888889</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>0.819444444444444</v>
+      </c>
+      <c r="H37" s="15" t="n">
         <f aca="false">IF(F37="","",G37-F37)</f>
-        <v/>
-      </c>
-      <c r="I37" s="16" t="str">
+        <v>0.152777777777778</v>
+      </c>
+      <c r="I37" s="16" t="n">
         <f aca="false">IF(H37="",IF(E37="","",IF(E37&lt;$C$2,"# Matin 1",IF(E37&gt;$D$2,"# Matin 2",E37))
 ),IF(E37="",IF(H37&lt;$C$2,"# AprèsMidi 1",IF(H37&gt;$D$2,"# AprèsMidi 2",H37)
 ),IF(H37&gt;$D$2,"# AprèsMidi 2",IF(E37&gt;$D$2,"# Matin 2",IF((F37-D37)&gt;$B$2,"# Repas 1", IF((F37-D37)&lt;$A$2,"# Repas 2",IF((E37+H37)&lt;$E$2,"# Jour 1",IF((E37+H37)&gt;$F$2,"# Jour 2",E37+H37))))))))</f>
-        <v/>
+        <v>0.291666666666667</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="14" t="n">
@@ -3305,31 +3309,23 @@
 ),IF(P37&gt;$D$2,"# AprèsMidi 2",IF(M37&gt;$D$2,"# Matin 2",IF((N37-L37)&gt;$B$2,"# Repas 1", IF((N37-L37)&lt;$A$2,"# Repas 2",IF((M37+P37)&lt;$E$2,"# Jour 1",IF((M37+P37)&gt;$F$2,"# Jour 2",M37+P37))))))))</f>
         <v>0.291666666666667</v>
       </c>
-      <c r="S37" s="14" t="n">
-        <v>0.517361111111111</v>
-      </c>
-      <c r="T37" s="14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="U37" s="15" t="n">
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="15" t="str">
         <f aca="false">IF(S37="","",T37-S37)</f>
-        <v>0.107638888888889</v>
-      </c>
-      <c r="V37" s="14" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="W37" s="14" t="n">
-        <v>0.819444444444444</v>
-      </c>
-      <c r="X37" s="15" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="15" t="str">
         <f aca="false">IF(V37="","",W37-V37)</f>
-        <v>0.152777777777778</v>
-      </c>
-      <c r="Y37" s="16" t="n">
+        <v/>
+      </c>
+      <c r="Y37" s="16" t="str">
         <f aca="false">IF(X37="",IF(U37="","",IF(U37&lt;$C$2,"# Matin 1",IF(U37&gt;$D$2,"# Matin 2",U37))
 ),IF(U37="",IF(X37&lt;$C$2,"# AprèsMidi 1",IF(X37&gt;$D$2,"# AprèsMidi 2",X37)
 ),IF(X37&gt;$D$2,"# AprèsMidi 2",IF(U37&gt;$D$2,"# Matin 2",IF((V37-T37)&gt;$B$2,"# Repas 1", IF((V37-T37)&lt;$A$2,"# Repas 2",IF((U37+X37)&lt;$E$2,"# Jour 1",IF((U37+X37)&gt;$F$2,"# Jour 2",U37+X37))))))))</f>
-        <v>0.260416666666667</v>
+        <v/>
       </c>
       <c r="AA37" s="14"/>
       <c r="AB37" s="14"/>
@@ -3356,24 +3352,24 @@
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="n">
-        <v>0.409722222222222</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="E38" s="15" t="n">
         <f aca="false">IF(C38="","",D38-C38)</f>
-        <v>0.173611111111111</v>
+        <v>0.125</v>
       </c>
       <c r="F38" s="14" t="n">
         <v>0.625</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>0.743055555555556</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="H38" s="15" t="n">
         <f aca="false">IF(F38="","",G38-F38)</f>
-        <v>0.118055555555556</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I38" s="16" t="n">
         <f aca="false">IF(H38="",IF(E38="","",IF(E38&lt;$C$2,"# Matin 1",IF(E38&gt;$D$2,"# Matin 2",E38))
@@ -3382,23 +3378,31 @@
         <v>0.291666666666667</v>
       </c>
       <c r="J38" s="3"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="15" t="str">
+      <c r="K38" s="14" t="n">
+        <v>0.409722222222222</v>
+      </c>
+      <c r="L38" s="14" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="M38" s="15" t="n">
         <f aca="false">IF(K38="","",L38-K38)</f>
-        <v/>
-      </c>
-      <c r="N38" s="14"/>
-      <c r="O38" s="14"/>
-      <c r="P38" s="15" t="str">
+        <v>0.173611111111111</v>
+      </c>
+      <c r="N38" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O38" s="14" t="n">
+        <v>0.743055555555556</v>
+      </c>
+      <c r="P38" s="15" t="n">
         <f aca="false">IF(N38="","",O38-N38)</f>
-        <v/>
-      </c>
-      <c r="Q38" s="16" t="str">
+        <v>0.118055555555556</v>
+      </c>
+      <c r="Q38" s="16" t="n">
         <f aca="false">IF(P38="",IF(M38="","",IF(M38&lt;$C$2,"# Matin 1",IF(M38&gt;$D$2,"# Matin 2",M38))
 ),IF(M38="",IF(P38&lt;$C$2,"# AprèsMidi 1",IF(P38&gt;$D$2,"# AprèsMidi 2",P38)
 ),IF(P38&gt;$D$2,"# AprèsMidi 2",IF(M38&gt;$D$2,"# Matin 2",IF((N38-L38)&gt;$B$2,"# Repas 1", IF((N38-L38)&lt;$A$2,"# Repas 2",IF((M38+P38)&lt;$E$2,"# Jour 1",IF((M38+P38)&gt;$F$2,"# Jour 2",M38+P38))))))))</f>
-        <v/>
+        <v>0.291666666666667</v>
       </c>
       <c r="S38" s="14" t="n">
         <v>0.517361111111111</v>
@@ -3450,52 +3454,44 @@
         <v>16</v>
       </c>
       <c r="B39" s="13"/>
-      <c r="C39" s="14" t="n">
-        <v>0.409722222222222</v>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="E39" s="15" t="n">
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="15" t="str">
         <f aca="false">IF(C39="","",D39-C39)</f>
-        <v>0.173611111111111</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G39" s="14" t="n">
-        <v>0.743055555555556</v>
-      </c>
-      <c r="H39" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="15" t="str">
         <f aca="false">IF(F39="","",G39-F39)</f>
-        <v>0.118055555555556</v>
-      </c>
-      <c r="I39" s="16" t="n">
+        <v/>
+      </c>
+      <c r="I39" s="16" t="str">
         <f aca="false">IF(H39="",IF(E39="","",IF(E39&lt;$C$2,"# Matin 1",IF(E39&gt;$D$2,"# Matin 2",E39))
 ),IF(E39="",IF(H39&lt;$C$2,"# AprèsMidi 1",IF(H39&gt;$D$2,"# AprèsMidi 2",H39)
 ),IF(H39&gt;$D$2,"# AprèsMidi 2",IF(E39&gt;$D$2,"# Matin 2",IF((F39-D39)&gt;$B$2,"# Repas 1", IF((F39-D39)&lt;$A$2,"# Repas 2",IF((E39+H39)&lt;$E$2,"# Jour 1",IF((E39+H39)&gt;$F$2,"# Jour 2",E39+H39))))))))</f>
-        <v>0.291666666666667</v>
+        <v/>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="14" t="n">
-        <v>0.486111111111111</v>
+        <v>0.409722222222222</v>
       </c>
       <c r="L39" s="14" t="n">
-        <v>0.625</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="M39" s="15" t="n">
         <f aca="false">IF(K39="","",L39-K39)</f>
-        <v>0.138888888888889</v>
+        <v>0.173611111111111</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>0.666666666666667</v>
+        <v>0.625</v>
       </c>
       <c r="O39" s="14" t="n">
-        <v>0.819444444444444</v>
+        <v>0.743055555555556</v>
       </c>
       <c r="P39" s="15" t="n">
         <f aca="false">IF(N39="","",O39-N39)</f>
-        <v>0.152777777777778</v>
+        <v>0.118055555555556</v>
       </c>
       <c r="Q39" s="16" t="n">
         <f aca="false">IF(P39="",IF(M39="","",IF(M39&lt;$C$2,"# Matin 1",IF(M39&gt;$D$2,"# Matin 2",M39))
@@ -3554,24 +3550,24 @@
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="n">
-        <v>0.409722222222222</v>
+        <v>0.486111111111111</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>0.583333333333333</v>
+        <v>0.625</v>
       </c>
       <c r="E40" s="15" t="n">
         <f aca="false">IF(C40="","",D40-C40)</f>
-        <v>0.173611111111111</v>
+        <v>0.138888888888889</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0.625</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0.743055555555556</v>
+        <v>0.819444444444444</v>
       </c>
       <c r="H40" s="15" t="n">
         <f aca="false">IF(F40="","",G40-F40)</f>
-        <v>0.118055555555556</v>
+        <v>0.152777777777778</v>
       </c>
       <c r="I40" s="16" t="n">
         <f aca="false">IF(H40="",IF(E40="","",IF(E40&lt;$C$2,"# Matin 1",IF(E40&gt;$D$2,"# Matin 2",E40))
@@ -3617,24 +3613,24 @@
         <v/>
       </c>
       <c r="AA40" s="14" t="n">
-        <v>0.458333333333333</v>
+        <v>0.409722222222222</v>
       </c>
       <c r="AB40" s="14" t="n">
-        <v>0.625</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="AC40" s="15" t="n">
         <f aca="false">IF(AA40="","",AB40-AA40)</f>
-        <v>0.166666666666667</v>
+        <v>0.173611111111111</v>
       </c>
       <c r="AD40" s="14" t="n">
-        <v>0.666666666666667</v>
+        <v>0.625</v>
       </c>
       <c r="AE40" s="14" t="n">
-        <v>0.819444444444444</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="AF40" s="15" t="n">
         <f aca="false">IF(AD40="","",AE40-AD40)</f>
-        <v>0.152777777777778</v>
+        <v>0.145833333333333</v>
       </c>
       <c r="AG40" s="16" t="n">
         <f aca="false">IF(AF40="",IF(AC40="","",IF(AC40&lt;$C$2,"# Matin 1",IF(AC40&gt;$D$2,"# Matin 2",AC40))
@@ -3748,7 +3744,7 @@
       <c r="P42" s="19"/>
       <c r="Q42" s="20" t="n">
         <f aca="false">SUM(Q35:Q41)</f>
-        <v>1.16666666666667</v>
+        <v>1.45833333333333</v>
       </c>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
@@ -3797,7 +3793,7 @@
       <c r="P43" s="3"/>
       <c r="Q43" s="22" t="str">
         <f aca="false">IF(Q42&lt;&gt;$I$2,"# Semaine 2","Ok Tps plein")</f>
-        <v># Semaine 2</v>
+        <v>Ok Tps plein</v>
       </c>
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>

--- a/Planning_ST_Antoine_12oct-1nov.xlsx
+++ b/Planning_ST_Antoine_12oct-1nov.xlsx
@@ -2170,17 +2170,17 @@
         <v>0.625</v>
       </c>
       <c r="O22" s="14" t="n">
-        <v>0.743055555555556</v>
+        <v>0.784722222222222</v>
       </c>
       <c r="P22" s="15" t="n">
         <f aca="false">IF(N22="","",O22-N22)</f>
-        <v>0.118055555555556</v>
+        <v>0.159722222222222</v>
       </c>
       <c r="Q22" s="16" t="n">
         <f aca="false">IF(P22="",IF(M22="","",IF(M22&lt;$C$2,"# Matin 1",IF(M22&gt;$D$2,"# Matin 2",M22))
 ),IF(M22="",IF(P22&lt;$C$2,"# AprèsMidi 1",IF(P22&gt;$D$2,"# AprèsMidi 2",P22)
 ),IF(P22&gt;$D$2,"# AprèsMidi 2",IF(M22&gt;$D$2,"# Matin 2",IF((N22-L22)&gt;$B$2,"# Repas 1", IF((N22-L22)&lt;$A$2,"# Repas 2",IF((M22+P22)&lt;$E$2,"# Jour 1",IF((M22+P22)&gt;$F$2,"# Jour 2",M22+P22))))))))</f>
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="S22" s="14"/>
       <c r="T22" s="14"/>
@@ -2352,17 +2352,17 @@
         <v>0.625</v>
       </c>
       <c r="O24" s="14" t="n">
-        <v>0.743055555555556</v>
+        <v>0.784722222222222</v>
       </c>
       <c r="P24" s="15" t="n">
         <f aca="false">IF(N24="","",O24-N24)</f>
-        <v>0.118055555555556</v>
+        <v>0.159722222222222</v>
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">IF(P24="",IF(M24="","",IF(M24&lt;$C$2,"# Matin 1",IF(M24&gt;$D$2,"# Matin 2",M24))
 ),IF(M24="",IF(P24&lt;$C$2,"# AprèsMidi 1",IF(P24&gt;$D$2,"# AprèsMidi 2",P24)
 ),IF(P24&gt;$D$2,"# AprèsMidi 2",IF(M24&gt;$D$2,"# Matin 2",IF((N24-L24)&gt;$B$2,"# Repas 1", IF((N24-L24)&lt;$A$2,"# Repas 2",IF((M24+P24)&lt;$E$2,"# Jour 1",IF((M24+P24)&gt;$F$2,"# Jour 2",M24+P24))))))))</f>
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="S24" s="14" t="n">
         <v>0.517361111111111</v>
@@ -2455,17 +2455,17 @@
         <v>0.625</v>
       </c>
       <c r="O25" s="14" t="n">
-        <v>0.743055555555556</v>
+        <v>0.784722222222222</v>
       </c>
       <c r="P25" s="15" t="n">
         <f aca="false">IF(N25="","",O25-N25)</f>
-        <v>0.118055555555556</v>
+        <v>0.159722222222222</v>
       </c>
       <c r="Q25" s="16" t="n">
         <f aca="false">IF(P25="",IF(M25="","",IF(M25&lt;$C$2,"# Matin 1",IF(M25&gt;$D$2,"# Matin 2",M25))
 ),IF(M25="",IF(P25&lt;$C$2,"# AprèsMidi 1",IF(P25&gt;$D$2,"# AprèsMidi 2",P25)
 ),IF(P25&gt;$D$2,"# AprèsMidi 2",IF(M25&gt;$D$2,"# Matin 2",IF((N25-L25)&gt;$B$2,"# Repas 1", IF((N25-L25)&lt;$A$2,"# Repas 2",IF((M25+P25)&lt;$E$2,"# Jour 1",IF((M25+P25)&gt;$F$2,"# Jour 2",M25+P25))))))))</f>
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="S25" s="14"/>
       <c r="T25" s="14"/>
@@ -2473,17 +2473,21 @@
         <f aca="false">IF(S25="","",T25-S25)</f>
         <v/>
       </c>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-      <c r="X25" s="15" t="str">
+      <c r="V25" s="14" t="n">
+        <v>0.611111111111111</v>
+      </c>
+      <c r="W25" s="14" t="n">
+        <v>0.819444444444444</v>
+      </c>
+      <c r="X25" s="15" t="n">
         <f aca="false">IF(V25="","",W25-V25)</f>
-        <v/>
-      </c>
-      <c r="Y25" s="16" t="str">
+        <v>0.208333333333333</v>
+      </c>
+      <c r="Y25" s="16" t="n">
         <f aca="false">IF(X25="",IF(U25="","",IF(U25&lt;$C$2,"# Matin 1",IF(U25&gt;$D$2,"# Matin 2",U25))
 ),IF(U25="",IF(X25&lt;$C$2,"# AprèsMidi 1",IF(X25&gt;$D$2,"# AprèsMidi 2",X25)
 ),IF(X25&gt;$D$2,"# AprèsMidi 2",IF(U25&gt;$D$2,"# Matin 2",IF((V25-T25)&gt;$B$2,"# Repas 1", IF((V25-T25)&lt;$A$2,"# Repas 2",IF((U25+X25)&lt;$E$2,"# Jour 1",IF((U25+X25)&gt;$F$2,"# Jour 2",U25+X25))))))))</f>
-        <v/>
+        <v>0.208333333333333</v>
       </c>
       <c r="AA25" s="14"/>
       <c r="AB25" s="14"/>
@@ -2509,11 +2513,15 @@
         <v>16</v>
       </c>
       <c r="B26" s="13"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="15" t="str">
+      <c r="C26" s="14" t="n">
+        <v>0.458333333333333</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E26" s="15" t="n">
         <f aca="false">IF(C26="","",D26-C26)</f>
-        <v/>
+        <v>0.208333333333333</v>
       </c>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
@@ -2521,11 +2529,11 @@
         <f aca="false">IF(F26="","",G26-F26)</f>
         <v/>
       </c>
-      <c r="I26" s="16" t="str">
+      <c r="I26" s="16" t="n">
         <f aca="false">IF(H26="",IF(E26="","",IF(E26&lt;$C$2,"# Matin 1",IF(E26&gt;$D$2,"# Matin 2",E26))
 ),IF(E26="",IF(H26&lt;$C$2,"# AprèsMidi 1",IF(H26&gt;$D$2,"# AprèsMidi 2",H26)
 ),IF(H26&gt;$D$2,"# AprèsMidi 2",IF(E26&gt;$D$2,"# Matin 2",IF((F26-D26)&gt;$B$2,"# Repas 1", IF((F26-D26)&lt;$A$2,"# Repas 2",IF((E26+H26)&lt;$E$2,"# Jour 1",IF((E26+H26)&gt;$F$2,"# Jour 2",E26+H26))))))))</f>
-        <v/>
+        <v>0.208333333333333</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="14" t="n">
@@ -2542,17 +2550,17 @@
         <v>0.625</v>
       </c>
       <c r="O26" s="14" t="n">
-        <v>0.743055555555556</v>
+        <v>0.784722222222222</v>
       </c>
       <c r="P26" s="15" t="n">
         <f aca="false">IF(N26="","",O26-N26)</f>
-        <v>0.118055555555556</v>
+        <v>0.159722222222222</v>
       </c>
       <c r="Q26" s="16" t="n">
         <f aca="false">IF(P26="",IF(M26="","",IF(M26&lt;$C$2,"# Matin 1",IF(M26&gt;$D$2,"# Matin 2",M26))
 ),IF(M26="",IF(P26&lt;$C$2,"# AprèsMidi 1",IF(P26&gt;$D$2,"# AprèsMidi 2",P26)
 ),IF(P26&gt;$D$2,"# AprèsMidi 2",IF(M26&gt;$D$2,"# Matin 2",IF((N26-L26)&gt;$B$2,"# Repas 1", IF((N26-L26)&lt;$A$2,"# Repas 2",IF((M26+P26)&lt;$E$2,"# Jour 1",IF((M26+P26)&gt;$F$2,"# Jour 2",M26+P26))))))))</f>
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="S26" s="14" t="n">
         <v>0.517361111111111</v>
@@ -2645,17 +2653,17 @@
         <v>0.625</v>
       </c>
       <c r="O27" s="14" t="n">
-        <v>0.743055555555556</v>
+        <v>0.784722222222222</v>
       </c>
       <c r="P27" s="15" t="n">
         <f aca="false">IF(N27="","",O27-N27)</f>
-        <v>0.118055555555556</v>
+        <v>0.159722222222222</v>
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">IF(P27="",IF(M27="","",IF(M27&lt;$C$2,"# Matin 1",IF(M27&gt;$D$2,"# Matin 2",M27))
 ),IF(M27="",IF(P27&lt;$C$2,"# AprèsMidi 1",IF(P27&gt;$D$2,"# AprèsMidi 2",P27)
 ),IF(P27&gt;$D$2,"# AprèsMidi 2",IF(M27&gt;$D$2,"# Matin 2",IF((N27-L27)&gt;$B$2,"# Repas 1", IF((N27-L27)&lt;$A$2,"# Repas 2",IF((M27+P27)&lt;$E$2,"# Jour 1",IF((M27+P27)&gt;$F$2,"# Jour 2",M27+P27))))))))</f>
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="S27" s="14"/>
       <c r="T27" s="14"/>
@@ -2802,7 +2810,7 @@
       <c r="H29" s="19"/>
       <c r="I29" s="20" t="n">
         <f aca="false">SUM(I22:I28)</f>
-        <v>1.45833333333333</v>
+        <v>1.66666666666667</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -2815,7 +2823,7 @@
       <c r="P29" s="19"/>
       <c r="Q29" s="20" t="n">
         <f aca="false">SUM(Q22:Q28)</f>
-        <v>1.45833333333333</v>
+        <v>1.66666666666667</v>
       </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
@@ -2827,7 +2835,7 @@
       <c r="X29" s="21"/>
       <c r="Y29" s="20" t="n">
         <f aca="false">SUM(Y22:Y28)</f>
-        <v>1.04166666666667</v>
+        <v>1.25</v>
       </c>
       <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
@@ -2853,7 +2861,7 @@
       <c r="H30" s="3"/>
       <c r="I30" s="22" t="str">
         <f aca="false">IF(I29&lt;&gt;$I$2,"# Semaine 2","Ok Tps plein")</f>
-        <v>Ok Tps plein</v>
+        <v># Semaine 2</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
@@ -2864,7 +2872,7 @@
       <c r="P30" s="3"/>
       <c r="Q30" s="22" t="str">
         <f aca="false">IF(Q29&lt;&gt;$I$2,"# Semaine 2","Ok Tps plein")</f>
-        <v>Ok Tps plein</v>
+        <v># Semaine 2</v>
       </c>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
